--- a/Luban/DataTables/Datas/AI/AI表.xlsx
+++ b/Luban/DataTables/Datas/AI/AI表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity\ProjectTinyRpg\Luban\DataTables\Datas\AI\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="11775" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="AI表" sheetId="3" r:id="rId1"/>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -68,9 +73,6 @@
   </si>
   <si>
     <t>VisionRange</t>
-  </si>
-  <si>
-    <t>AggroRange</t>
   </si>
   <si>
     <t>ThreatTime</t>
@@ -95,9 +97,6 @@
   </si>
   <si>
     <t>视野</t>
-  </si>
-  <si>
-    <t>攻击范围</t>
   </si>
   <si>
     <t>警惕值</t>
@@ -792,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -805,9 +804,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1172,21 +1168,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="19.45" customWidth="1"/>
-    <col min="3" max="4" width="11.1916666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.9916666666667" customWidth="1"/>
-    <col min="6" max="6" width="14.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="26.3" customWidth="1"/>
-    <col min="8" max="8" width="11.1916666666667" customWidth="1"/>
-    <col min="9" max="9" width="10.1" customWidth="1"/>
-    <col min="10" max="11" width="9" customWidth="1"/>
+    <col min="3" max="3" width="11.1916666666667" customWidth="1"/>
+    <col min="4" max="4" width="19.9916666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="26.3" customWidth="1"/>
+    <col min="7" max="7" width="11.1916666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.1" customWidth="1"/>
+    <col min="9" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1197,26 +1193,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
     </row>
-    <row r="2" ht="58.5" spans="1:11">
-      <c r="A2" s="7" t="s">
+    <row r="2" ht="58.5" spans="1:10">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="9" t="s">
@@ -1225,108 +1220,96 @@
       <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:10">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="B3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="71.25" spans="1:11">
-      <c r="A3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="13" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="14" t="s">
+      <c r="B4" s="15">
+        <v>100001</v>
+      </c>
+      <c r="C4" s="16">
+        <v>6</v>
+      </c>
+      <c r="D4" s="15">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
+      <c r="F4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="17">
+        <v>3</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="16">
-        <v>100001</v>
-      </c>
-      <c r="C4" s="17">
-        <v>10</v>
-      </c>
-      <c r="D4" s="16">
-        <v>8</v>
-      </c>
-      <c r="E4" s="16">
+    <row r="5" spans="1:10">
+      <c r="A5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="15">
+        <v>100002</v>
+      </c>
+      <c r="C5" s="16">
+        <v>6</v>
+      </c>
+      <c r="D5" s="15">
         <v>3</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="18">
+      <c r="G5" s="17">
         <v>3</v>
       </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="16">
-        <v>100002</v>
-      </c>
-      <c r="C5" s="17">
-        <v>10</v>
-      </c>
-      <c r="D5" s="16">
-        <v>8</v>
-      </c>
-      <c r="E5" s="16">
-        <v>3</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="18">
-        <v>3</v>
-      </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
